--- a/outputs/daily/hr_rankings_2026-09-20_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-20_full.xlsx
@@ -5013,7 +5013,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>40.1</v>
+        <v>39.1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>22.9</v>
+        <v>21.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -9411,27 +9411,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>663457</t>
+          <t>671732</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9474,54 +9474,58 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>47.5</v>
+        <v>37.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>49.2</v>
+        <v>54.2</v>
       </c>
       <c r="R33" t="n">
-        <v>42.2</v>
+        <v>40.6</v>
       </c>
       <c r="S33" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T33" t="n">
         <v>80</v>
       </c>
       <c r="U33" t="n">
-        <v>36.3</v>
+        <v>74.5</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9546,22 +9550,22 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.6% barrel, 25.8 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9571,112 +9575,112 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>91.86</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>101.7802</t>
+          <t>101.8414</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4231</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1563</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>73.26</t>
+          <t>73.63</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>90.93</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.4169</t>
+          <t>0.3973</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9687,27 +9691,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9717,17 +9721,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sandy Alcantara</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>645261</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9750,26 +9754,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>37.2</v>
+        <v>58</v>
       </c>
       <c r="Q34" t="n">
-        <v>54.2</v>
+        <v>36.9</v>
       </c>
       <c r="R34" t="n">
-        <v>40.6</v>
+        <v>47.1</v>
       </c>
       <c r="S34" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T34" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>74.5</v>
+        <v>63.8</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9783,7 +9787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9821,12 +9825,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9841,122 +9845,122 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.6% barrel, 25.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 22.7 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>53.13</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>93.09</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>101.8414</t>
+          <t>104.4668</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.495</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1563</t>
+          <t>0.2072</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>73.63</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1787</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3973</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9967,22 +9971,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>663457</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10002,12 +10006,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sandy Alcantara</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>645261</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -10030,50 +10034,42 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>58</v>
+        <v>47.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>36.9</v>
+        <v>49.2</v>
       </c>
       <c r="R35" t="n">
-        <v>47.1</v>
+        <v>42.2</v>
       </c>
       <c r="S35" t="n">
         <v>93.2</v>
       </c>
       <c r="T35" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>63.8</v>
+        <v>34.9</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -10081,7 +10077,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10101,142 +10101,142 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 22.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>53.13</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>93.09</t>
+          <t>91.86</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>104.4668</t>
+          <t>101.7802</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>0.4231</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.2072</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>73.26</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>35.33</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1787</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>90.93</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.4169</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1428</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -11449,7 +11449,7 @@
         <v>75</v>
       </c>
       <c r="U40" t="n">
-        <v>15.3</v>
+        <v>14.1</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -12536,7 +12536,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>33.9</v>
+        <v>32</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -13887,47 +13887,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>608369</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-20T18:35:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Spencer Miles</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>693686</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13954,22 +13954,22 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>61.8</v>
+        <v>56.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>11.9</v>
+        <v>21.9</v>
       </c>
       <c r="R49" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="S49" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T49" t="n">
         <v>80</v>
       </c>
       <c r="U49" t="n">
-        <v>48.5</v>
+        <v>57.2</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -14004,7 +14004,7 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr"/>
@@ -14021,12 +14021,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -14036,112 +14036,112 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Contact streak: 11/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>92.13</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>102.614</t>
+          <t>102.1395</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.5095</t>
+          <t>0.4947</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.2462</t>
+          <t>0.2185</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3678</t>
+          <t>0.3635</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>56.51</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.1817</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.31</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3229</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.1192</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14167,47 +14167,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>608369</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T18:35:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Game Over</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Spencer Miles</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693686</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14234,22 +14234,22 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>56.1</v>
+        <v>61.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="R50" t="n">
-        <v>41.6</v>
+        <v>42.1</v>
       </c>
       <c r="S50" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T50" t="n">
         <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>57.2</v>
+        <v>46.9</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -14284,7 +14284,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
@@ -14316,112 +14316,112 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Contact streak: 11/29 over last 7 games</t>
+          <t>Last 7 games: 9/29, 1 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>92.13</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>102.1395</t>
+          <t>102.614</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4947</t>
+          <t>0.5095</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.2185</t>
+          <t>0.2462</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3635</t>
+          <t>0.3678</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>56.51</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1817</t>
+          <t>0.2034</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>86.31</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.3229</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.1192</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
         <v>50</v>
       </c>
       <c r="U52" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
@@ -24243,12 +24243,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>672640</t>
+          <t>805300</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -24306,11 +24306,11 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>30.1</v>
+        <v>20.8</v>
       </c>
       <c r="Q86" t="n">
         <v>43</v>
@@ -24319,13 +24319,13 @@
         <v>47.1</v>
       </c>
       <c r="S86" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T86" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U86" t="n">
-        <v>34.9</v>
+        <v>81.7</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -24377,27 +24377,27 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24407,67 +24407,67 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>100.1719</t>
+          <t>98.6208</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.4242</t>
+          <t>0.3657</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1204</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3286</t>
+          <t>0.3239</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.1325</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
@@ -24523,27 +24523,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>805300</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T20:07:00Z</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -24553,17 +24553,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -24572,7 +24572,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24586,26 +24586,26 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="Q87" t="n">
-        <v>43</v>
+        <v>44.6</v>
       </c>
       <c r="R87" t="n">
-        <v>47.1</v>
+        <v>49.7</v>
       </c>
       <c r="S87" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T87" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U87" t="n">
-        <v>81.7</v>
+        <v>32</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -24657,142 +24657,142 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>35.28</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>98.6208</t>
+          <t>97.71</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.3657</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.3239</t>
+          <t>0.2792</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.68</t>
         </is>
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1833</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>34.09</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI87" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ87" t="inlineStr"/>
@@ -24803,27 +24803,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>672640</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-20T20:07:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -24838,12 +24838,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24866,26 +24866,26 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>21.3</v>
+        <v>30.1</v>
       </c>
       <c r="Q88" t="n">
-        <v>44.6</v>
+        <v>43</v>
       </c>
       <c r="R88" t="n">
-        <v>49.7</v>
+        <v>47.1</v>
       </c>
       <c r="S88" t="n">
         <v>100</v>
       </c>
       <c r="T88" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U88" t="n">
-        <v>32</v>
+        <v>33.7</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24937,142 +24937,142 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>97.71</t>
+          <t>100.1719</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.4242</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.2792</t>
+          <t>0.3286</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>33.63</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1325</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>50</v>
       </c>
       <c r="U91" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -25792,7 +25792,7 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
@@ -29003,52 +29003,52 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>668800</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Andrew Knizner</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T23:20:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Jack Dreyer</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>676263</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L103" t="n">
@@ -29066,26 +29066,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>13.4</v>
+        <v>16.9</v>
       </c>
       <c r="Q103" t="n">
-        <v>34.3</v>
+        <v>43.1</v>
       </c>
       <c r="R103" t="n">
-        <v>63.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S103" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T103" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U103" t="n">
-        <v>58.7</v>
+        <v>54.9</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -29137,12 +29137,12 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 6.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 18.3 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
@@ -29167,112 +29167,112 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>85.53</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>97.1405</t>
+          <t>99.1565</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.3454</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0981</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.2899</t>
+          <t>0.2918</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.1319</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>40.17</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.1377</t>
+          <t>0.1651</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -29283,56 +29283,56 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>668800</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Andrew Knizner</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-20T23:20:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Jack Dreyer</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>676263</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -29346,26 +29346,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>16.9</v>
+        <v>13.4</v>
       </c>
       <c r="Q104" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
       <c r="R104" t="n">
-        <v>67.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="S104" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T104" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U104" t="n">
-        <v>54.9</v>
+        <v>55.6</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29417,12 +29417,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29432,12 +29432,12 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Contact streak: 7/19 over last 7 games</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 18.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 6.1 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -29447,112 +29447,112 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>85.53</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>99.1565</t>
+          <t>97.1405</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3454</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.0981</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.2918</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1319</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1651</t>
+          <t>0.1377</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -35435,47 +35435,47 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>673962</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-20T18:35:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Spencer Miles</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>693686</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -35498,26 +35498,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>37.2</v>
+        <v>34.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>11.9</v>
+        <v>21.9</v>
       </c>
       <c r="R126" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="S126" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T126" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U126" t="n">
-        <v>63.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -35552,7 +35552,7 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr"/>
@@ -35569,27 +35569,27 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
@@ -35599,97 +35599,97 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>100.402</t>
+          <t>99.7373</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.4329</t>
+          <t>0.3819</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.1585</t>
+          <t>0.1463</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3136</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.31</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3229</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.1192</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr">
@@ -35699,12 +35699,12 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr"/>
@@ -35715,47 +35715,47 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>673962</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T18:35:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Game Over</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Spencer Miles</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693686</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -35778,26 +35778,26 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>34.2</v>
+        <v>37.2</v>
       </c>
       <c r="Q127" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="R127" t="n">
-        <v>41.6</v>
+        <v>42.1</v>
       </c>
       <c r="S127" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T127" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U127" t="n">
-        <v>71.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35832,7 +35832,7 @@
       <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr"/>
@@ -35849,27 +35849,27 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -35879,97 +35879,97 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>99.7373</t>
+          <t>100.402</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.3819</t>
+          <t>0.4329</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1463</t>
+          <t>0.1585</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.3136</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>86.31</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.3229</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1192</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr">
@@ -35979,12 +35979,12 @@
       </c>
       <c r="BH127" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -36555,24 +36555,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>683011</t>
+          <t>694374</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Tim Tawa</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>2026-09-20T20:10:00Z</t>
@@ -36585,17 +36585,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Corbin Burnes</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>669203</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -36618,50 +36618,42 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>25.5</v>
+        <v>40.2</v>
       </c>
       <c r="Q130" t="n">
-        <v>54.5</v>
+        <v>49.2</v>
       </c>
       <c r="R130" t="n">
         <v>42.2</v>
       </c>
       <c r="S130" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T130" t="n">
         <v>50</v>
       </c>
       <c r="U130" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -36669,7 +36661,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC130" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36689,7 +36685,7 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
@@ -36704,112 +36700,112 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>98.8902</t>
+          <t>100.6567</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.3581</t>
+          <t>0.3932</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.1613</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.2982</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.1195</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.93</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.4081</t>
+          <t>0.4169</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.1839</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr">
@@ -36835,24 +36831,24 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>694374</t>
+          <t>683011</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tim Tawa</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>2026-09-20T20:10:00Z</t>
@@ -36865,17 +36861,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Corbin Burnes</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>669203</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -36884,7 +36880,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -36898,54 +36894,58 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>40.2</v>
+        <v>25.5</v>
       </c>
       <c r="Q131" t="n">
-        <v>49.2</v>
+        <v>54.5</v>
       </c>
       <c r="R131" t="n">
         <v>42.2</v>
       </c>
       <c r="S131" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T131" t="n">
         <v>50</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y131" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36965,12 +36965,12 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -36980,112 +36980,112 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>100.6567</t>
+          <t>98.8902</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.3932</t>
+          <t>0.3581</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.1613</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.2982</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>33.01</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1195</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>90.93</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.4169</t>
+          <t>0.4081</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1839</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
@@ -38000,7 +38000,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>78</v>
       </c>
       <c r="U135" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
@@ -38100,7 +38100,7 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
@@ -38231,32 +38231,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>676439</t>
+          <t>807726</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>John Peck</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Delayed Start</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -38266,21 +38266,21 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Matt Wilkinson</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>683363</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -38294,17 +38294,17 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>27.1</v>
+        <v>34.4</v>
       </c>
       <c r="Q136" t="n">
-        <v>50.9</v>
+        <v>44.8</v>
       </c>
       <c r="R136" t="n">
-        <v>63.1</v>
+        <v>53.6</v>
       </c>
       <c r="S136" t="n">
         <v>44.8</v>
@@ -38313,7 +38313,7 @@
         <v>50</v>
       </c>
       <c r="U136" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -38365,12 +38365,12 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
@@ -38380,127 +38380,127 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>98.7756</t>
+          <t>98.866</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3475</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.1206</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.3058</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.4293</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1573</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -38511,32 +38511,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>807726</t>
+          <t>676439</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>John Peck</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Delayed Start</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -38546,17 +38546,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Matt Wilkinson</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>683363</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -38574,17 +38574,17 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>34.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q137" t="n">
-        <v>44.8</v>
+        <v>50.9</v>
       </c>
       <c r="R137" t="n">
-        <v>53.6</v>
+        <v>63.1</v>
       </c>
       <c r="S137" t="n">
         <v>44.8</v>
@@ -38593,7 +38593,7 @@
         <v>50</v>
       </c>
       <c r="U137" t="n">
-        <v>8.5</v>
+        <v>0.8</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr"/>
@@ -38645,12 +38645,12 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -38660,127 +38660,127 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>98.866</t>
+          <t>98.7756</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3475</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1206</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3058</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>32.73</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.085</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.4293</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.1573</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH137" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr"/>
@@ -38840,7 +38840,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>50</v>
       </c>
       <c r="U138" t="n">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
@@ -38940,7 +38940,7 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>50</v>
       </c>
       <c r="U151" t="n">
-        <v>36</v>
+        <v>33.9</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -42580,7 +42580,7 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
@@ -43140,7 +43140,7 @@
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
@@ -55715,7 +55715,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>40.1</v>
+        <v>39.1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -56802,7 +56802,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>22.9</v>
+        <v>21.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -56902,7 +56902,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
